--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAVALETE LATERAL- 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAVALETE LATERAL- 02_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -453,11 +448,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,11 +468,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,11 +484,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,11 +504,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,11 +520,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -570,11 +540,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -591,11 +556,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -616,11 +576,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -641,11 +596,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -666,11 +616,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -691,11 +636,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -716,24 +656,26 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
